--- a/QCM1_1_CH.xlsx
+++ b/QCM1_1_CH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AA11D21-CDA4-4781-8188-724EE72881BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C39745-BAA6-4387-9875-854612335FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="335">
   <si>
     <t>Question</t>
   </si>
@@ -63,15 +63,6 @@
     <t>OptionE</t>
   </si>
   <si>
-    <t>Acides • Bases</t>
-  </si>
-  <si>
-    <t>Q1. Un acide selon Bronsted</t>
-  </si>
-  <si>
-    <t>Un spèce chimique capable de céder un électron</t>
-  </si>
-  <si>
     <t>Une espèce chimique capable de capter un électron</t>
   </si>
   <si>
@@ -84,16 +75,7 @@
     <t>À déterminer</t>
   </si>
   <si>
-    <t>Q2. Une base selon Bronsted •</t>
-  </si>
-  <si>
     <t>Une espèce chimique capable de céder un électron</t>
-  </si>
-  <si>
-    <t>Q3 L'équation de la réaction modélisant une transformation acido-basique •</t>
-  </si>
-  <si>
-    <t>AH{aq) + BH+aq) $\rightleftharpoons$ $B_{}^{}(aq)$ + $A_{}^{-}(aq)$</t>
   </si>
   <si>
     <t>$AH_{}^{}(aq)$ + $A_{}^{-}(aq)$  BH+aq) + $B_{}^{}(aq)$</t>
@@ -1098,6 +1080,21 @@
   </si>
   <si>
     <t>0,0126 mS. cm-1</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Acides - Bases&lt;/b&gt;&lt;/center&gt;&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>Un acide selon Bronsted :</t>
+  </si>
+  <si>
+    <t>Une base selon Bronsted :</t>
+  </si>
+  <si>
+    <t>L'équation de la réaction modélisant une transformation acido-basique :</t>
+  </si>
+  <si>
+    <t>AH_{aq} + BH^{+}_{aq} $\rightleftharpoons$ $B_{aq}$ + $A_{aq}^{-}$</t>
   </si>
 </sst>
 </file>
@@ -1634,29 +1631,29 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>17</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="5"/>
@@ -1664,26 +1661,26 @@
     <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3" s="12" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="5"/>
@@ -1691,26 +1688,26 @@
     <row r="4" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
       <c r="B4" s="12" t="s">
-        <v>21</v>
+        <v>333</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>22</v>
+        <v>334</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="5"/>
@@ -1718,26 +1715,26 @@
     <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="12" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="5"/>
@@ -1745,26 +1742,26 @@
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="12" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
@@ -1772,26 +1769,26 @@
     <row r="7" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="12" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -1799,26 +1796,26 @@
     <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
       <c r="B8" s="12" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -1826,26 +1823,26 @@
     <row r="9" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="12" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -1853,26 +1850,26 @@
     <row r="10" spans="1:11" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="B10" s="12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -1880,26 +1877,26 @@
     <row r="11" spans="1:11" ht="102" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="12" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1907,26 +1904,26 @@
     <row r="12" spans="1:11" ht="178.5" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="12" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -1934,26 +1931,26 @@
     <row r="13" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="12" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -1961,26 +1958,26 @@
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -1988,26 +1985,26 @@
     <row r="15" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
       <c r="B15" s="12" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -2015,26 +2012,26 @@
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -2042,1284 +2039,1284 @@
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
       <c r="B17" s="12" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="12" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="12" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="12" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="12" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="12" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="12" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="12" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="153" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="12" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="12" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="12" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="12" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="12" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="12" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
       <c r="B35" s="12" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="12" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="11"/>
       <c r="B37" s="12" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="12" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F38" s="12"/>
       <c r="G38" s="12"/>
       <c r="H38" s="12"/>
       <c r="I38" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A39" s="11"/>
       <c r="B39" s="12" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A40" s="11"/>
       <c r="B40" s="12" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C40" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E40" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="H40" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="F40" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="G40" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="H40" s="12" t="s">
-        <v>204</v>
-      </c>
       <c r="I40" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="12" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
       <c r="I41" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="242.25" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
       <c r="B42" s="12" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A43" s="11"/>
       <c r="B43" s="12" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A44" s="11"/>
       <c r="B44" s="12" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A45" s="11"/>
       <c r="B45" s="12" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A46" s="11"/>
       <c r="B46" s="12" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="12"/>
       <c r="H46" s="12"/>
       <c r="I46" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A47" s="11"/>
       <c r="B47" s="12" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C47" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A48" s="11"/>
       <c r="B48" s="12" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G48" s="12"/>
       <c r="H48" s="12"/>
       <c r="I48" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A49" s="11"/>
       <c r="B49" s="12" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="H49" s="12"/>
       <c r="I49" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A50" s="11"/>
       <c r="B50" s="12" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A51" s="11"/>
       <c r="B51" s="12" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="F51" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="E51" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>257</v>
-      </c>
       <c r="G51" s="12" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A52" s="11"/>
       <c r="B52" s="12" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A53" s="11"/>
       <c r="B53" s="12" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="H53" s="12"/>
       <c r="I53" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
       <c r="B54" s="12" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="11"/>
       <c r="B55" s="12" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="H55" s="12"/>
       <c r="I55" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A56" s="11"/>
       <c r="B56" s="12" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C56" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="H56" s="12"/>
       <c r="I56" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="11"/>
       <c r="B57" s="12" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="H57" s="12"/>
       <c r="I57" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A58" s="11"/>
       <c r="B58" s="12" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="H58" s="12"/>
       <c r="I58" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A59" s="11"/>
       <c r="B59" s="12" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C59" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="H59" s="12"/>
       <c r="I59" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A60" s="11"/>
       <c r="B60" s="12" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="G60" s="12"/>
       <c r="H60" s="12"/>
       <c r="I60" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A61" s="11"/>
       <c r="B61" s="12" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C61" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H61" s="12"/>
       <c r="I61" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="11"/>
       <c r="B62" s="12" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C62" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="H62" s="12"/>
       <c r="I62" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A63" s="11"/>
       <c r="B63" s="12" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C63" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="H63" s="12"/>
       <c r="I63" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A64" s="11"/>
       <c r="B64" s="12" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C64" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="H64" s="12"/>
       <c r="I64" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A65" s="11"/>
       <c r="B65" s="12" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C65" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H65" s="12"/>
       <c r="I65" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A66" s="11"/>
       <c r="B66" s="12" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C66" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="H66" s="12"/>
       <c r="I66" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A67" s="11"/>
       <c r="B67" s="12" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C67" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="H67" s="12"/>
       <c r="I67" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/QCM1_1_CH.xlsx
+++ b/QCM1_1_CH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA627340-EDF2-4D90-9414-EDB455AE9E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD772AF6-DA33-436D-8716-A62FD4064656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="361">
   <si>
     <t>Question</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Une espèce chimique capable de céder un électron</t>
   </si>
   <si>
-    <t>1-solution d'hydroxyde de sodium, 2-solution acide méthanoïque, 3-agitateur</t>
-  </si>
-  <si>
     <t>Rouge de méthyle (4,4-6,2)</t>
   </si>
   <si>
@@ -195,9 +192,6 @@
     <t>$AH_{(aq)} + BH^+_{(aq)} \rightleftharpoons B_{(aq)} + A^-_{(aq)}$</t>
   </si>
   <si>
-    <t>$AH_{(aq)} + A^-_{(aq)} \rightleftharpoons BH^+_{(aq)} + B_{(aq)}$</t>
-  </si>
-  <si>
     <t>$BH^+_{(aq)} + B_{(aq)} \rightleftharpoons A^-_{(aq)} + AH_{(aq)}$</t>
   </si>
   <si>
@@ -216,18 +210,6 @@
     <t>$A^-_{(aq)} + H_2O_{(l)} \rightleftharpoons AH_{(aq)} + H_3O^+_{(aq)}$</t>
   </si>
   <si>
-    <t>$C_6H_{10}O_{6(aq)} / C_6H_8O_{6(aq)}$ et $H_3O^+_{(aq)} / H_2O_{(l)}$</t>
-  </si>
-  <si>
-    <t>$C_6H_8O_{6(aq)} / C_6H_{10}O_{6(aq)}$ et $H_2O_{(l)} / H_3O^+_{(aq)}$</t>
-  </si>
-  <si>
-    <t>$C_6H_{10}O_{6(aq)} / C_6H_8O_{6(aq)}$ et $H_2O_{(l)} / HO^-_{(aq)}$</t>
-  </si>
-  <si>
-    <t>$C_6H_8O_{6(aq)} / C_6H_{10}O_{6(aq)}$ et $HO^-_{(aq)} / H_2O_{(l)}$</t>
-  </si>
-  <si>
     <t>$H_2O_{(l)} / HO^-_{(aq)}$ et $H_3O^+_{(aq)} / H_2O_{(l)}$</t>
   </si>
   <si>
@@ -261,9 +243,6 @@
     <t>$NH_{3(aq)} + H_3O^+_{(aq)} \rightarrow NH^+_{4(aq)} + H_2O_{(l)}$</t>
   </si>
   <si>
-    <t>$NH_{3(aq)} + HBr \rightarrow NH^+_{4(aq)} + H_2O_{(aq)}$</t>
-  </si>
-  <si>
     <t>$KOH + HCl \rightarrow K^+_{(aq)} + Cl^-_{(aq)}$</t>
   </si>
   <si>
@@ -321,9 +300,6 @@
     <t>$CH_3COOH_{(aq)} + H_2O_{(l)} \rightleftharpoons CH_3COO^-_{(aq)} + H_3O^+_{(aq)}$</t>
   </si>
   <si>
-    <t>$CH_3COO^-_{(aq)} + H_2O_{(l)} \rightleftharpoons CH_3COOH_{(aq)} + HO^-_{(aq)}$</t>
-  </si>
-  <si>
     <t>$2,5\cdot 10^{-4}$</t>
   </si>
   <si>
@@ -348,30 +324,6 @@
     <t>$6,03\cdot 10^{-10}$</t>
   </si>
   <si>
-    <t>$\tau_2 = 2,5\cdot 10^{-4}$</t>
-  </si>
-  <si>
-    <t>$\tau_2 = 2,5\cdot 10^{-5}$</t>
-  </si>
-  <si>
-    <t>$\tau_2 = 8\cdot 10^{-4}$</t>
-  </si>
-  <si>
-    <t>$\tau_2 = 2,5\cdot 10^{-3}$</t>
-  </si>
-  <si>
-    <t>$\tau = 0,75$</t>
-  </si>
-  <si>
-    <t>$\tau = 0,5$</t>
-  </si>
-  <si>
-    <t>$\tau = 0,1$</t>
-  </si>
-  <si>
-    <t>$\tau = 0,25$</t>
-  </si>
-  <si>
     <t>$3,8$</t>
   </si>
   <si>
@@ -417,9 +369,6 @@
     <t>$C_A = \frac{1+\tau}{\tau^2} \cdot 10^{pK_A}$</t>
   </si>
   <si>
-    <t>$C_A = \frac{\tau^2}{1-\tau}$</t>
-  </si>
-  <si>
     <t>$C_A = \frac{1-\tau}{\tau^2} \cdot 10^{-pK_A}$</t>
   </si>
   <si>
@@ -438,33 +387,6 @@
     <t>$C_A = 1,4\cdot 10^{-3}\text{ mol}\cdot\text{L}^{-1}$</t>
   </si>
   <si>
-    <t>$pH = 2,55$</t>
-  </si>
-  <si>
-    <t>$pH = 3,23$</t>
-  </si>
-  <si>
-    <t>$pH = 2,8$</t>
-  </si>
-  <si>
-    <t>$pH = 5,8$</t>
-  </si>
-  <si>
-    <t>$pH = 8,55$</t>
-  </si>
-  <si>
-    <t>1-solution acide méthanoïque, 2-solution d'hydroxyde de sodium, 3-pH-mètre</t>
-  </si>
-  <si>
-    <t>1-burette graduée, 2-solution acide méthanoïque, 3-agitateur</t>
-  </si>
-  <si>
-    <t>1-solution d'hydroxyde de sodium, 2-solution acide méthanoïque, 3-sonde de pH</t>
-  </si>
-  <si>
-    <t>1-solution d'hydroxyde de sodium, 2-solution acide méthanoïque, 3-pH-mètre</t>
-  </si>
-  <si>
     <t>$V_A = 10\text{ mL}$</t>
   </si>
   <si>
@@ -495,30 +417,9 @@
     <t>$C_2H_5CO_2H_{(aq)} + H_2O_{(l)} \rightleftharpoons H_3O^+_{(aq)} + C_2H_5CO_{2(aq)}^-$</t>
   </si>
   <si>
-    <t>$K = \frac{[H_3O^+][C_2H_5CO_2^-]}{[C_2H_5CO_2H]}$</t>
-  </si>
-  <si>
-    <t>$K = \frac{[C_2H_5CO_2H]}{[H_3O^+][C_2H_5CO_2^-]}$</t>
-  </si>
-  <si>
-    <t>$K = \frac{[H_3O^+][C_2H_5CO_2^-]}{[C_2H_5CO_2H][H_2O]}$</t>
-  </si>
-  <si>
-    <t>$K = \frac{[C_2H_5CO_2^-]}{[C_2H_5CO_2H]}$</t>
-  </si>
-  <si>
-    <t>$pH = pK_A + \log\left(\frac{10^{-pH}}{C_A - 10^{-pH}}\right)$</t>
-  </si>
-  <si>
-    <t>$pH = pK_A + \log\left(\frac{C_A - 10^{-pH}}{10^{-pH}}\right)$</t>
-  </si>
-  <si>
     <t>$pH = pK_A - \log\left(\frac{10^{-pH}}{C_A - 10^{-pH}}\right)$</t>
   </si>
   <si>
-    <t>$pH = pK_A + \log\left(\frac{10^{-pH}}{C_A}\right)$</t>
-  </si>
-  <si>
     <t>$\tau = \frac{1}{1 + 10^{pH - pK_A}}$</t>
   </si>
   <si>
@@ -528,21 +429,6 @@
     <t>$\tau = \frac{1}{1 + 10^{pK_A - pH}}$</t>
   </si>
   <si>
-    <t>$\tau = \frac{1}{1 + 10^{pK_A - 2pH}}$</t>
-  </si>
-  <si>
-    <t>$C_A = 5\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$</t>
-  </si>
-  <si>
-    <t>$C_A = 5\cdot 10^{-3}\text{ mol}\cdot\text{L}^{-1}$</t>
-  </si>
-  <si>
-    <t>$C_A = 1\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$</t>
-  </si>
-  <si>
-    <t>$C_A = 1\cdot 10^{-3}\text{ mol}\cdot\text{L}^{-1}$</t>
-  </si>
-  <si>
     <t>$C_2H_5CO_2H_{(aq)} + HO^-_{(aq)} \rightleftharpoons C_2H_5CO_{2(aq)}^- + H_2O_{(l)}$</t>
   </si>
   <si>
@@ -573,12 +459,6 @@
     <t>$[C_2H_5CO_2H] = \frac{C_B \cdot V_{BE}}{V_A + V_{BE}}$</t>
   </si>
   <si>
-    <t>$[C_2H_5CO_2H] = \frac{C_B \cdot V_{BE}}{2(V_A + V_B)}$</t>
-  </si>
-  <si>
-    <t>$[C_2H_5CO_2H] = \frac{C_B \cdot V_{BE}}{2(V_A + V_{BE})}$</t>
-  </si>
-  <si>
     <t>$pH = 7$</t>
   </si>
   <si>
@@ -591,36 +471,15 @@
     <t>$pH = 7,8$</t>
   </si>
   <si>
-    <t>Contexte pour les questions 38-40 (Page suivante)</t>
-  </si>
-  <si>
-    <t>information</t>
-  </si>
-  <si>
     <t>$pH_E &lt; 7$</t>
   </si>
   <si>
-    <t>$pH_E = 7$</t>
-  </si>
-  <si>
     <t>$pH_E &gt; 7$</t>
   </si>
   <si>
     <t>$pH_E &gt; 14$</t>
   </si>
   <si>
-    <t>$V_{éq} = 1\text{ mL}$</t>
-  </si>
-  <si>
-    <t>$V_{éq} = 10\text{ mL}$</t>
-  </si>
-  <si>
-    <t>$V_{éq} = 0,1\text{ mL}$</t>
-  </si>
-  <si>
-    <t>$V_{éq} = 15\text{ mL}$</t>
-  </si>
-  <si>
     <t>faux</t>
   </si>
   <si>
@@ -858,9 +717,6 @@
     <t>$12,6\text{ mS}\cdot\text{m}^{-1}$</t>
   </si>
   <si>
-    <t>Les deux couples intervenants dans cette transformation : $C_6H_8O_{6(aq)} + H_2O_{(l)} \rightleftharpoons ...$</t>
-  </si>
-  <si>
     <t>Les deux couples intervenants dans cette transformation : $2H_2O_{(l)} \rightleftharpoons HO^-_{(aq)} + H_3O^+_{(aq)}$</t>
   </si>
   <si>
@@ -918,9 +774,6 @@
     <t>L'équation chimique de la réaction entre l'acide propanoïque et l'eau s'écrit :</t>
   </si>
   <si>
-    <t>L'expression de la constante d'équilibre $K$ est :</t>
-  </si>
-  <si>
     <t>L'expression de $pH$ est :</t>
   </si>
   <si>
@@ -931,9 +784,6 @@
   </si>
   <si>
     <t>La solution obtenue à l'équivalence est :</t>
-  </si>
-  <si>
-    <t>Le volume de la solution $(S_B)$ versé pour atteindre l'équivalence acido-basique est $V_{BE} = 9,8\text{ mL}$. La valeur de $C_A$ vaut :</t>
   </si>
   <si>
     <t>La valeur du pH du mélange dans ce cas est :</t>
@@ -1028,96 +878,6 @@
   <si>
     <t>&lt;center&gt;&lt;b&gt;Le pH d'une solution&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
 On prépare une solution aqueuse d'acide chlorhydrique $S_A$, en dissolvant un volume $V = 120\text{ mL}$ du gaz $HCl$ dans $50\text{ cm}^3$ d'eau distillée. $Vm = 24\text{ L}\cdot\text{mol}^{-1}$.</t>
-  </si>
-  <si>
-    <t>On dilue la solution $S_A$ 100 fois pour obtenir une solution $S'_A$.
-Le pH' de la solution $S'_A$ est :</t>
-  </si>
-  <si>
-    <t>A un volume $V_A = 10\text{ mL}$ de la solution $S_A$ de concentration $C_A = 10^{-2}\text{ mol}\cdot\text{L}^{-1}$, on ajoute un volume $V_B = 20\text{ mL}$ d'une solution d'ammoniac $NH_3$ de concentration $C_B = 10^{-2}\text{ mol}\cdot\text{L}^{-1}$.
-On donne $pK_A(NH_4^+ / NH_3) = 9,2$.
-Le pH du mélange est :</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;L'éthanoate de sodium&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-La masse molaire de l'éthanoate de sodium $M(CH_3COONa) = 82\text{ g}\cdot\text{mol}^{-1}$.
-$K_e = 10^{-14}$ ; $K_A(CH_3COOH/CH_3COO^-) = 1,6\cdot 10^{-5}$ ; $10^{0,4} = 2,5$ ; $\log 2 = 0,3$
-On dissout dans l'eau distillée des cristaux d'éthanoate de sodium de masse $m = 410\text{ mg}$ pour obtenir une solution $S_1$ de volume $V = 500\text{ mL}$ et de concentration $C_1$ et $pH_1 = 8,4$.</t>
-  </si>
-  <si>
-    <t>On prend un volume $V_1$ de la solution $S_1$ et on y ajoute une quantité d'eau distillée pour obtenir une solution $S_2$ de concentration $C_2 = 10^{-3}\text{ mol}\cdot\text{L}^{-1}$.
-Le taux d'avancement final $\tau_2$ est :</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Equimolaire&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-On mélange une quantité de matière $n_0$ d'une solution d'éthanoate de sodium et la même quantité de matière $n_0$ d'une solution aqueuse d'acide méthanoïque $HCOOH$ on modélise la transformation qui a eu lieu par une réaction chimique d'équation : $CH_3COO^-_{(aq)} + HCOOH_{(aq)} \rightleftharpoons CH_3COOH_{(aq)} + HCOO^-_{(aq)}$. La constante d'équilibre $K$ associée à cette équation est : $K = 10$</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Etude d'une solution aqueuse d'acide méthanoïque&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-A partir de la solution précédente $(S)$, on prépare une solution aqueuse $(S_A)$ de concentration molaire $C_A$.
-Le taux d'avancement final de la réaction entre l'acide méthanoïque et l'eau dans ce cas vaut $\tau = 0,21$.
-Donnée : $pK_A(HCO_2H_{(aq)} / HCO_{2(aq)}^-) = 3,8$</t>
-  </si>
-  <si>
-    <t>En utilisant le dispositif schématisé sur la figure (1), on dose le volume $V_A$ de la solution $(S_A)$ par une solution aqueuse $(S_B)$ d'hydroxyde de sodium $Na^+_{(aq)} + HO^-_{(aq)}$ de concentration molaire $C_B = 10^{-2}\text{ mol}\cdot\text{L}^{-1}$. La courbe de la figure 2 représente la variation du pH du mélange en fonction du volume $V_B$ de la solution $(S_B)$ versé au cours du dosage.
-Nommer les éléments du dispositif numérotés 1, 2, 3.</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Etude d'une solution aqueuse d'acide propanoïque&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-On dispose d'une solution aqueuse $(S_A)$ d'acide propanoïque $C_2H_5CO_2H$ de concentration molaire $C_A$ et de volume $V$. La mesure du pH de la solution donne la valeur de $pH = 3,59$.
-Données : $pK_A(C_2H_5CO_2H_{(aq)} / C_2H_5CO_{2(aq)}^-) = 4,85$ ;</t>
-  </si>
-  <si>
-    <t>Pour s'assurer de la valeur de $C_A$, on dose le volume $V_A = 20\text{ mL}$ de la solution $(S_A)$ par une solution aqueuse $(S_B)$ d'hydroxyde de sodium $Na^+_{(aq)} + HO^-_{(aq)}$ de concentration molaire $C_B = 10^{-2}\text{ mol}\cdot\text{L}^{-1}$.
-L'équation de la réaction du dosage :</t>
-  </si>
-  <si>
-    <t>On considère le mélange lorsque le volume de la solution $(S_B)$ versé est $V_B = \frac{V_{BE}}{2}$.
-L'expression de la concentration effective de $[C_2H_5CO_2H]$ vaut :</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Dosage d'un acide faible&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-Dosage d'un acide faible de $pK_A = 1,5$ par la soude de concentration $0,10\text{ mol}\cdot\text{L}^{-1}$.
-Le couple acide base est noté $AH / A^-$ ; la concentration de la solution est $C = 1,0\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$ et le pH de la solution est égal à $2,1$. On donne : $10^{0,6} = 3,98$.
-On dose $V = 10\text{ mL}$ de la solution acide par la soude de concentration $C_B = 0,10\text{ mol}\cdot\text{L}^{-1}$.</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Mélanges&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-On mélange $V\text{ mL}$ d'acide nitrique de concentration $C$ et $V\text{ mL}$ d'acide chlorhydrique de concentration $C$.
-On donne $C = 5\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$. On donne : $\log(5) \approx 0,7$</t>
-  </si>
-  <si>
-    <t>A 50 mL d'une solution obtenue en dissolvant $0,164\text{ g}$ de $CH_3COONa$ dans 100 mL d'eau distillée, on ajoute 50 mL de solution de $HCl$ à $0,06\text{ mol}\cdot\text{L}^{-1}$. On donne : $\log(2) \approx 0,3$.
-(On donne $pK_A(CH_3COOH/CH_3COO^-) = 4,7$ et $M(CH_3COONa) = 82\text{ g}\cdot\text{mol}^{-1}$).
-Le pH de la solution obtenue :</t>
-  </si>
-  <si>
-    <t>On mélange 6 mL de soude $NaOH$ à $0,01\text{ mol}\cdot\text{L}^{-1}$ et 100 mL d'une solution à $0,01\text{ mol}\cdot\text{L}^{-1}$ d'un monoacide faible $AH$. Le pH de la solution est $5,75$. On donne : $\log(100/6) \approx 1,2$.
-Le $pK_A$ du monoacide $AH$ est :</t>
-  </si>
-  <si>
-    <t>On mélange 50 mL d'une solution de $HNO_3$ à $1\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$ et 50 mL d'une solution de $HCl$ à $x\text{ mol}\cdot\text{L}^{-1}$.
-Le pH du mélange est $1,2$. On donne : $10^{-1,2} = 6,3\cdot 10^{-2}$.
-La valeur de $x$ est :</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Le pourcentage massique en soude NaOH&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-On désire déterminer le pourcentage massique en soude $NaOH$ d'un déboucheur de canalisation. On dilue 50 fois la solution commerciale de ce déboucheur. On obtient $1,0\text{ L}$ de solution diluée.
-On dose $V = 10,0\text{ mL}$ de cette solution par une solution d'acide chlorhydrique de concentration $C_A = 0,10\text{ mol}\cdot\text{L}^{-1}$. $V_E = 5,0\text{ mL}$.
-Données : densité du déboucheur : $d = 1,1$ ; $11 \times 9 = 100$ ; $M(NaOH) = 40\text{ g}\cdot\text{mol}^{-1}$</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Solution commerciale d'hydroxyde de sodium&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-Solution commerciale $S_0$ d'hydroxyde de sodium :
-Densité $d = 1,33$ ;
-Pourcentage massique $30\text{ \%}$.
-$V = 5,0\text{ mL}$ de cette solution sont versés dans une fiole jaugée de 500 mL ;
-On complète avec de l'eau distillée jusqu'au trait de jauge. On note $S_1$ cette solution diluée.
-On dose $20,0\text{ mL}$ d'une solution d'acide méthanoïque par la solution $S_1$. $V_E = 16,2\text{ mL}$.</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Phénate de sodium&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-On dissout 0,2 mol de phénate de sodium $C_6H_5ONa$ dans 1 L d'eau. On donne $pK_{A1}(C_6H_5OH/C_6H_5O^-) = 10$ et $pK_{A2}(CH_3COOH/CH_3COO^-) = 4,8$.</t>
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;Phénate de sodium et l'acide éthanoïque&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
@@ -1156,6 +916,261 @@
 Un mélange de 2 litres de soude à $10^{-4}\text{ mol}\cdot\text{L}^{-1}$ et de 10 mL d'acide chlorhydrique à $2\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$.
 On donne les conductivités ioniques molaires ($\text{S}\cdot\text{m}^2\cdot\text{mol}^{-1}$) à 25 °C :
 $\lambda_{Na^+} = 5\cdot 10^{-3}$ ; $\lambda_{Cl^-} = 7,6\cdot 10^{-3}$ ; $\lambda_{HO^-} = 19,8\cdot 10^{-3}$ ; $\lambda_{H_3O^+} = 34,9\cdot 10^{-3}$.</t>
+  </si>
+  <si>
+    <t>$AH_{(aq)} + A^-_{(aq)} \rightleftharpoons BH^+_{(aq)} + B^-_{(aq)}$</t>
+  </si>
+  <si>
+    <t>Les deux couples intervenants dans cette transformation : $C_6H_8O_{6(aq)} + H_2O_{(l)} \rightleftharpoons C_6H_7O^-_{6(aq)} + H_3O^+_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$C_6H_{7}O^-_{6(aq)} / C_6H_8O_{6(aq)}$ et $H_3O^+_{(aq)} / H_2O_{(l)}$</t>
+  </si>
+  <si>
+    <t>$C_6H_8O_{6(aq)} / C_6H_{7}O^-_{6(aq)}$ et $H_2O_{(l)} / H_3O^+_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$C_6H_{7}O^-_{6(aq)} / C_6H_8O_{6(aq)}$ et $H_2O_{(l)} / H_3O^+_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$C_6H_8O_{6(aq)} / C_6H_{7}O^-_{6(aq)}$ et $H_3O^+_{(aq)} / H_2O_{(l)}$</t>
+  </si>
+  <si>
+    <t>$NH_{3(aq)} + HBr \rightarrow NH^+_{4(aq)} + H_3O^+_{(aq)}$</t>
+  </si>
+  <si>
+    <t>On dilue la solution $S_A$ 100 fois pour obtenir une solution $S'_A$.
+&lt;br&gt;Le pH' de la solution $S'_A$ est :</t>
+  </si>
+  <si>
+    <t>A un volume $V_A = 10\text{ mL}$ de la solution $S_A$ de concentration $C_A = 10^{-2}\text{ mol}\cdot\text{L}^{-1}$, on ajoute un volume $V_B = 20\text{ mL}$ d'une solution d'ammoniac $NH_3$ de concentration $C_B = 10^{-2}\text{ mol}\cdot\text{L}^{-1}$.
+&lt;br&gt;On donne $pK_A(NH_4^+ / NH_3) = 9,2$.
+&lt;br&gt;Le pH du mélange est :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;L'éthanoate de sodium&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+La masse molaire de l'éthanoate de sodium $M(CH_3COONa) = 82\text{ g}\cdot\text{mol}^{-1}$.
+&lt;br&gt;$K_e = 10^{-14}$ ; $K_{A1}(CH_3COOH/CH_3COO^-) = 1,6\cdot 10^{-5}$ ; $\quad$ $10^{0,4} = 2,5$ ; $\quad$ $\log 2 = 0,3$
+&lt;br&gt;On dissout dans l'eau distillée des cristaux d'éthanoate de sodium de masse $m = 410\text{ mg}$ pour obtenir une solution $S_1$ de volume $V = 500\text{ mL}$ et de concentration $C_1$ et $pH_1 = 8,4$.</t>
+  </si>
+  <si>
+    <t>$CH_3COO^-_{(aq)} + H_3O^+_{(aq)} \rightleftharpoons CH_3COOH_{(aq)} + H_2O_{(l)}$</t>
+  </si>
+  <si>
+    <t>On prend un volume $V_1$ de la solution $S_1$ et on y ajoute une quantité d'eau distillée pour obtenir une solution $S_2$ de concentration $C_2 = 10^{-3}\text{ mol}\cdot\text{L}^{-1}$.
+&lt;br&gt;Le taux d'avancement final $\tau_2$ est :</t>
+  </si>
+  <si>
+    <t>$\tau_2 \approx 2\cdot 10^{-4}$</t>
+  </si>
+  <si>
+    <t>$\tau_2 \approx 1,5\cdot 10^{-4}$</t>
+  </si>
+  <si>
+    <t>$\tau_2 \approx 8\cdot 10^{-4}$</t>
+  </si>
+  <si>
+    <t>$\tau_2 \approx 7,5\cdot 10^{-5}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Equimolaire&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On mélange une quantité de matière $n_0$ d'une solution d'éthanoate de sodium et la même quantité de matière $n_0$ d'une solution aqueuse d'acide méthanoïque $HCOOH$.
+&lt;br&gt;On modélise la transformation qui a eu lieu par une réaction chimique d'équation : 
+&lt;br&gt;$CH_3COO^-_{(aq)} + HCOOH_{(aq)} \rightleftharpoons CH_3COOH_{(aq)} + HCOO^-_{(aq)}$. 
+&lt;br&gt;La constante d'équilibre $K$ associée à cette équation est : $K = 10$</t>
+  </si>
+  <si>
+    <t>$\tau \approx 0,75$</t>
+  </si>
+  <si>
+    <t>$\tau \approx 1$</t>
+  </si>
+  <si>
+    <t>$\tau \approx 0,5$</t>
+  </si>
+  <si>
+    <t>$\tau \approx 0,1$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Etude d'une solution aqueuse d'acide méthanoïque&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+A partir de la solution précédente $(S)$, on prépare une solution aqueuse $(S_A)$ de concentration molaire $C_A$.
+Le taux d'avancement final de la réaction entre l'acide méthanoïque et l'eau dans ce cas vaut $\tau = 0,21$.
+&lt;br&gt;Donnée : $pK_A(HCO_2H_{(aq)} / HCO_{2(aq)}^-) = 3,8$</t>
+  </si>
+  <si>
+    <t>$C_A = \frac{\tau^2}{1-\tau} \cdot 10^{pK_A}$</t>
+  </si>
+  <si>
+    <t>$pH \approx 2,55$</t>
+  </si>
+  <si>
+    <t>$pH \approx 3,23$</t>
+  </si>
+  <si>
+    <t>$pH \approx 2,8$</t>
+  </si>
+  <si>
+    <t>$pH \approx 5,8$</t>
+  </si>
+  <si>
+    <t>$pH \approx 8,55$</t>
+  </si>
+  <si>
+    <t>En utilisant le dispositif schématisé sur la figure (1), on dose le volume $V_A$ de la solution $(S_A)$ par une solution aqueuse $(S_B)$ d'hydroxyde de sodium $Na^+_{(aq)} + HO^-_{(aq)}$ de concentration molaire $C_B = 10^{-2}\text{ mol}\cdot\text{L}^{-1}$. 
+La courbe de la figure 2 représente la variation du pH du mélange en fonction du volume $V_B$ de la solution $(S_B)$ versé au cours du dosage.
+&lt;br&gt;Nommer les éléments du dispositif numérotés 1, 2, 3.</t>
+  </si>
+  <si>
+    <t>1-solution d'hydroxyde de sodium,&lt;br&gt; 2-solution acide méthanoïque, &lt;br&gt;3-agitateur</t>
+  </si>
+  <si>
+    <t>1-solution acide méthanoïque, &lt;br&gt;2-solution d'hydroxyde de sodium, &lt;br&gt;3-pH-mètre</t>
+  </si>
+  <si>
+    <t>1-burette graduée, &lt;br&gt;2-solution acide méthanoïque, &lt;br&gt;3-agitateur</t>
+  </si>
+  <si>
+    <t>1-solution d'hydroxyde de sodium, &lt;br&gt;2-solution acide méthanoïque, &lt;br&gt;3-sonde de pH</t>
+  </si>
+  <si>
+    <t>1-solution d'hydroxyde de sodium, &lt;br&gt;2-solution acide méthanoïque, &lt;br&gt;3-pH-mètre</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Etude d'une solution aqueuse d'acide propanoïque&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On dispose d'une solution aqueuse $(S_A)$ d'acide propanoïque $C_2H_5CO_2H$ de concentration molaire $C_A$ et de volume $V$. La mesure du pH de la solution donne la valeur de $pH = 3,59$.
+&lt;br&gt;Données : $pK_A(C_2H_5CO_2H_{(aq)} / C_2H_5CO_{2(aq)}^-) = 4,85$ ;</t>
+  </si>
+  <si>
+    <t>L'expression de la constante d'acidité $K_A$ du couple (C_2H_5CO_2H_{(aq)} / C_2H_5CO_{2(aq)}^-) est :</t>
+  </si>
+  <si>
+    <t>$K_A = \frac{[C_2H_5CO_2^-]}{[C_2H_5CO_2H]}$</t>
+  </si>
+  <si>
+    <t>$K_A = \frac{[C_2H_5CO_2^-]}{C_A - [C_2H_5CO_2H]}$</t>
+  </si>
+  <si>
+    <t>$K_A = \frac{[C_2H_5CO_2^-]}{10^PH \cdot [C_2H_5CO_2H]}$</t>
+  </si>
+  <si>
+    <t>$K_A = \frac{[C_2H_5CO_2^-] \cdot 10^PH}{[C_2H_5CO_2H]}$</t>
+  </si>
+  <si>
+    <t>$pH = pK_A + \log\left(10^{pH} \cdot C_A - 1)\right)$</t>
+  </si>
+  <si>
+    <t>$pH = pK_A + \log\left(\frac{1}{10^{pH} \cdot C_A - 1})\right)$</t>
+  </si>
+  <si>
+    <t>$pH = pK_A + \log\left(\frac{1}{10^{-pH} \cdot C_A - 1})\right)$</t>
+  </si>
+  <si>
+    <t>Pour s'assurer de la valeur de $C_A$, on dose le volume $V_A = 20\text{ mL}$ de la solution $(S_A)$ par une solution aqueuse $(S_B)$ d'hydroxyde de sodium $Na^+_{(aq)} + HO^-_{(aq)}$ de concentration molaire $C_B = 10^{-2}\text{ mol}\cdot\text{L}^{-1}$.
+&lt;br&gt;L'équation de la réaction du dosage :</t>
+  </si>
+  <si>
+    <t>Le volume de la solution $(S_B)$ versé pour atteindre l'équivalence acido-basique est $V_{BE} = 9,8\text{ mL}$. 
+&lt;br&gt;La valeur de $C_A$ vaut :</t>
+  </si>
+  <si>
+    <t>On considère le mélange lorsque le volume de la solution $(S_B)$ versé est $V_B = \frac{V_{BE}}{2}$.
+&lt;br&gt;L'expression de la concentration effective de $[C_2H_5CO_2H]$ vaut :</t>
+  </si>
+  <si>
+    <t>$[C_2H_5CO_2H] = \frac{C_B \cdot V_{BE}}{V_A + 2V_{BE}}$</t>
+  </si>
+  <si>
+    <t>$[C_2H_5CO_2H] = \frac{C_B \cdot V_{BE}}{2V_A + V_{BE}}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Dosage d'un acide faible&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+Dosage d'un acide faible de $pK_A = 1,5$ par la soude de concentration $0,10\text{ mol}\cdot\text{L}^{-1}$.
+&lt;br&gt;Le couple acide base est noté $AH / A^-$ ; la concentration de la solution est $C = 1,0\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$ et le pH de la solution est égal à $2,1$. 
+&lt;br&gt;On donne : $10^{0,6} = 3,98$.
+&lt;br&gt;On dose $V = 10\text{ mL}$ de la solution acide par la soude de concentration $C_B = 0,10\text{ mol}\cdot\text{L}^{-1}$.</t>
+  </si>
+  <si>
+    <t>$pH_E \approx 7$</t>
+  </si>
+  <si>
+    <t>$V_{Béq} = 1\text{ mL}$</t>
+  </si>
+  <si>
+    <t>$V_{Béq} = 10\text{ mL}$</t>
+  </si>
+  <si>
+    <t>$V_{Béq} = 0,1\text{ mL}$</t>
+  </si>
+  <si>
+    <t>$V_{Béq} = 15\text{ mL}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Mélanges&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On mélange $V\text{ mL}$ d'acide nitrique de concentration $C$ et $V\text{ mL}$ d'acide chlorhydrique de concentration $C$.
+&lt;br&gt;On donne $C = 5\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$. $\quad$  $\log(5) \approx 0,7$</t>
+  </si>
+  <si>
+    <t>A 50 mL d'une solution obtenue en dissolvant $0,164\text{ g}$ de $CH_3COONa$ dans 100 mL d'eau distillée, on ajoute 50 mL de solution de $HCl$ à $0,06\text{ mol}\cdot\text{L}^{-1}$. 
+&lt;br&gt;On donne : $\log(2) \approx 0,3$. $\quad$ $pK_A(CH_3COOH/CH_3COO^-) = 4,7$ et $M(CH_3COONa) = 82\text{ g}\cdot\text{mol}^{-1}$).
+&lt;br&gt;Le pH de la solution obtenue :</t>
+  </si>
+  <si>
+    <t>On mélange 76 mL de soude $NaOH$ à $0,01\text{ mol}\cdot\text{L}^{-1}$ et 100 mL d'une solution à $0,01\text{ mol}\cdot\text{L}^{-1}$ d'un monoacide faible $AH$. Le pH de la solution est $5,75$. 
+&lt;br&gt;On donne : $\log(19/6) \approx 0,52$.
+&lt;br&gt;Le $pK_A$ du monoacide $AH$ est :</t>
+  </si>
+  <si>
+    <t>$5,52$</t>
+  </si>
+  <si>
+    <t>$5,75$</t>
+  </si>
+  <si>
+    <t>On mélange 50 mL d'une solution de $HNO_3$ à $1\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$ et 50 mL d'une solution de $HCl$ à $x\text{ mol}\cdot\text{L}^{-1}$.
+Le pH du mélange est $1,82$. 
+&lt;br&gt;On donne : $10^{-1,82} = 1,51\cdot 10^{-2}$.
+&lt;br&gt;La valeur de $x$ est :</t>
+  </si>
+  <si>
+    <t>$0,15$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Le pourcentage massique en soude NaOH&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On désire déterminer le pourcentage massique en soude $NaOH$ d'un déboucheur de canalisation. On dilue 50 fois la solution commerciale de ce déboucheur. On obtient $1,0\text{ L}$ de solution diluée.
+&lt;br&gt;On dose $V = 10,0\text{ mL}$ de cette solution par une solution d'acide chlorhydrique de concentration $C_A = 0,10\text{ mol}\cdot\text{L}^{-1}$. $V_E = 5,0\text{ mL}$.
+&lt;br&gt;Données : densité du déboucheur : $d = 1,1$ ; $\quad$ $11 \times 9 \approx 100$ ; $\quad$ $M(NaOH) \approx 40\text{ g}\cdot\text{mol}^{-1}$</t>
+  </si>
+  <si>
+    <t>$5\text{ mol}\cdot\text{L}^{-1}$</t>
+  </si>
+  <si>
+    <t>$1\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$</t>
+  </si>
+  <si>
+    <t>$5\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Solution commerciale d'hydroxyde de sodium&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+Solution commerciale $S_0$ d'hydroxyde de sodium :
+&lt;br&gt; * Densité $d = 1,33$ ;
+&lt;br&gt; * Pourcentage massique $30\text{ \%}$.
+&lt;br&gt; * $V = 5,0\text{ mL}$ de cette solution sont versés dans une fiole jaugée de 500 mL ;
+&lt;br&gt;On complète avec de l'eau distillée jusqu'au trait de jauge. On note $S_1$ cette solution diluée.
+On dose $20,0\text{ mL}$ d'une solution d'acide méthanoïque par la solution $S_1$. $V_E = 16,2\text{ mL}$.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Phénate de sodium&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On dissout 0,2 mol de phénate de sodium $C_6H_5ONa$ dans 1 L d'eau. 
+&lt;br&gt;On donne $pK_{A1}(C_6H_5OH/C_6H_5O^-) = 10$ et $pK_{A2}(CH_3COOH/CH_3COO^-) = 4,8$.</t>
+  </si>
+  <si>
+    <t>$5,6 \cdot 10^{-4}$</t>
+  </si>
+  <si>
+    <t>$2 \cdot 10^{4}$</t>
+  </si>
+  <si>
+    <t>La concentration, à l'équilibre, en phénol en $\text{mol}\cdot\text{L}^{-1}$ est :</t>
   </si>
 </sst>
 </file>
@@ -1692,10 +1707,10 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>332</v>
+        <v>282</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>3</v>
@@ -1720,7 +1735,7 @@
     <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>3</v>
@@ -1745,22 +1760,22 @@
     <row r="4" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="14" t="s">
+      <c r="E4" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="F4" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="G4" s="14" t="s">
         <v>56</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>58</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="12"/>
@@ -1770,47 +1785,47 @@
     <row r="5" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="10"/>
       <c r="B5" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="G5" s="14" t="s">
         <v>60</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>62</v>
       </c>
       <c r="H5" s="14"/>
       <c r="I5" s="12"/>
       <c r="J5" s="6"/>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="10"/>
       <c r="B6" s="14" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>63</v>
+        <v>293</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>64</v>
+        <v>294</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>65</v>
+        <v>295</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>66</v>
+        <v>296</v>
       </c>
       <c r="H6" s="14"/>
       <c r="I6" s="12"/>
@@ -1820,22 +1835,22 @@
     <row r="7" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="14" t="s">
-        <v>278</v>
+        <v>230</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="12"/>
@@ -1845,22 +1860,22 @@
     <row r="8" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="14" t="s">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="12"/>
@@ -1870,22 +1885,22 @@
     <row r="9" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="14" t="s">
-        <v>280</v>
+        <v>232</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
@@ -1895,22 +1910,22 @@
     <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="B10" s="14" t="s">
-        <v>281</v>
+        <v>233</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H10" s="14"/>
       <c r="I10" s="12"/>
@@ -1920,22 +1935,22 @@
     <row r="11" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="14" t="s">
-        <v>282</v>
+        <v>234</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="12"/>
@@ -1944,25 +1959,25 @@
     </row>
     <row r="12" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>333</v>
+        <v>283</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="9"/>
@@ -1972,22 +1987,22 @@
     <row r="13" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="13" t="s">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="9"/>
@@ -1997,22 +2012,22 @@
     <row r="14" spans="1:11" ht="102" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="13" t="s">
-        <v>335</v>
+        <v>299</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="9"/>
@@ -2021,25 +2036,25 @@
     </row>
     <row r="15" spans="1:11" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>285</v>
+        <v>237</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>98</v>
+        <v>301</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="9"/>
@@ -2049,22 +2064,22 @@
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="14" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="12"/>
@@ -2074,22 +2089,22 @@
     <row r="17" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="14" t="s">
-        <v>287</v>
+        <v>239</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="12"/>
@@ -2097,47 +2112,47 @@
     <row r="18" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="13" t="s">
-        <v>337</v>
+        <v>302</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>107</v>
+        <v>303</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>108</v>
+        <v>304</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>109</v>
+        <v>305</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>110</v>
+        <v>306</v>
       </c>
       <c r="H18" s="13"/>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="153" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>338</v>
+        <v>307</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>111</v>
+        <v>308</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>112</v>
+        <v>309</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>113</v>
+        <v>310</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>114</v>
+        <v>311</v>
       </c>
       <c r="H19" s="13"/>
       <c r="I19" s="9"/>
@@ -2145,22 +2160,22 @@
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
       <c r="B20" s="14" t="s">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="12"/>
@@ -2168,47 +2183,47 @@
     <row r="21" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="14" t="s">
-        <v>289</v>
+        <v>241</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="12"/>
     </row>
     <row r="22" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>290</v>
+        <v>242</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="9"/>
@@ -2216,172 +2231,172 @@
     <row r="23" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
       <c r="B23" s="14" t="s">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>130</v>
+        <v>313</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="I23" s="12"/>
     </row>
     <row r="24" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
       <c r="B24" s="14" t="s">
-        <v>292</v>
+        <v>244</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="I24" s="12"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="10"/>
       <c r="B25" s="14" t="s">
-        <v>293</v>
+        <v>245</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>137</v>
+        <v>314</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>138</v>
+        <v>315</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>139</v>
+        <v>316</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>140</v>
+        <v>317</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>141</v>
+        <v>318</v>
       </c>
       <c r="I25" s="12"/>
     </row>
     <row r="26" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" s="13" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>16</v>
+        <v>320</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>142</v>
+        <v>321</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>143</v>
+        <v>322</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>144</v>
+        <v>323</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>145</v>
+        <v>324</v>
       </c>
       <c r="I26" s="9"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="10"/>
       <c r="B27" s="14" t="s">
-        <v>294</v>
+        <v>246</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="I27" s="12"/>
     </row>
     <row r="28" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="10"/>
       <c r="B28" s="14" t="s">
-        <v>295</v>
+        <v>247</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="F28" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="14" t="s">
-        <v>19</v>
-      </c>
       <c r="G28" s="14" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="H28" s="14"/>
       <c r="I28" s="12"/>
     </row>
     <row r="29" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>296</v>
+        <v>248</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="H29" s="13"/>
       <c r="I29" s="9"/>
@@ -2389,45 +2404,45 @@
     <row r="30" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
       <c r="B30" s="14" t="s">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>156</v>
+        <v>327</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>157</v>
+        <v>328</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>158</v>
+        <v>329</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>159</v>
+        <v>330</v>
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="10"/>
       <c r="B31" s="14" t="s">
-        <v>298</v>
+        <v>249</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>160</v>
+        <v>331</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>161</v>
+        <v>332</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>163</v>
+        <v>333</v>
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="12"/>
@@ -2435,22 +2450,22 @@
     <row r="32" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="10"/>
       <c r="B32" s="14" t="s">
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="12"/>
@@ -2458,22 +2473,22 @@
     <row r="33" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
       <c r="B33" s="14" t="s">
-        <v>300</v>
+        <v>251</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="12"/>
@@ -2481,22 +2496,22 @@
     <row r="34" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A34" s="7"/>
       <c r="B34" s="13" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="9"/>
@@ -2504,19 +2519,19 @@
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
       <c r="B35" s="14" t="s">
-        <v>301</v>
+        <v>252</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="F35" s="14" t="s">
         <v>21</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>22</v>
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
@@ -2525,22 +2540,22 @@
     <row r="36" spans="1:9" ht="51" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
       <c r="B36" s="14" t="s">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>177</v>
+        <v>139</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="H36" s="14"/>
       <c r="I36" s="12"/>
@@ -2548,22 +2563,22 @@
     <row r="37" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
       <c r="B37" s="13" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>182</v>
+        <v>337</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>183</v>
+        <v>338</v>
       </c>
       <c r="H37" s="13"/>
       <c r="I37" s="9"/>
@@ -2571,62 +2586,70 @@
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
       <c r="B38" s="14" t="s">
-        <v>303</v>
+        <v>253</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>184</v>
+        <v>144</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="H38" s="14"/>
       <c r="I38" s="12"/>
     </row>
     <row r="39" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
+        <v>339</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>150</v>
+      </c>
       <c r="H39" s="13"/>
       <c r="I39" s="9"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
       <c r="B40" s="14" t="s">
-        <v>304</v>
+        <v>255</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>190</v>
+        <v>341</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>191</v>
+        <v>342</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>192</v>
+        <v>343</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>193</v>
+        <v>344</v>
       </c>
       <c r="H40" s="14"/>
       <c r="I40" s="12"/>
@@ -2634,419 +2657,443 @@
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
       <c r="B41" s="14" t="s">
-        <v>305</v>
+        <v>256</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>194</v>
+        <v>22</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="F41" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="G41" s="14" t="s">
-        <v>197</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
       <c r="H41" s="14"/>
       <c r="I41" s="12"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="12"/>
-    </row>
-    <row r="43" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
+    <row r="42" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
         <v>345</v>
       </c>
+      <c r="B42" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H42" s="13"/>
+      <c r="I42" s="9"/>
+    </row>
+    <row r="43" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="7"/>
       <c r="B43" s="13" t="s">
-        <v>307</v>
+        <v>346</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>199</v>
+        <v>153</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="H43" s="13"/>
+        <v>81</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>157</v>
+      </c>
       <c r="I43" s="9"/>
     </row>
-    <row r="44" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
       <c r="B44" s="13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>202</v>
+        <v>349</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>200</v>
+        <v>348</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="I44" s="9"/>
     </row>
-    <row r="45" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
       <c r="B45" s="13" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>205</v>
+        <v>351</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
+        <v>162</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>164</v>
+      </c>
       <c r="I45" s="9"/>
     </row>
-    <row r="46" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
+    <row r="46" spans="1:9" ht="178.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>352</v>
+      </c>
       <c r="B46" s="13" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>209</v>
+        <v>166</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>210</v>
+        <v>167</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="H46" s="13"/>
+        <v>168</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>169</v>
+      </c>
       <c r="I46" s="9"/>
     </row>
-    <row r="47" spans="1:9" ht="178.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="G47" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="H47" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="I47" s="9"/>
+    <row r="47" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="10"/>
+      <c r="B47" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="I47" s="12"/>
     </row>
     <row r="48" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
       <c r="B48" s="14" t="s">
-        <v>309</v>
+        <v>260</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>217</v>
+        <v>172</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
+        <v>173</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="I48" s="12"/>
     </row>
-    <row r="49" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
       <c r="B49" s="14" t="s">
-        <v>310</v>
+        <v>261</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>219</v>
+        <v>23</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="F49" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="G49" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="H49" s="14" t="s">
-        <v>223</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
       <c r="I49" s="12"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="10"/>
-      <c r="B50" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="14" t="s">
+    <row r="50" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="I50" s="9"/>
+    </row>
+    <row r="51" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="E51" s="13">
+        <v>45</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="H51" s="13">
+        <v>1</v>
+      </c>
+      <c r="I51" s="9"/>
+    </row>
+    <row r="52" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="10"/>
+      <c r="B52" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="I52" s="12"/>
+    </row>
+    <row r="53" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="F53" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E50" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="12"/>
-    </row>
-    <row r="51" spans="1:9" ht="153" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="G51" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="H51" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="I51" s="9"/>
-    </row>
-    <row r="52" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="9"/>
-    </row>
-    <row r="53" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="10"/>
-      <c r="B53" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="F53" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="G53" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H53" s="14"/>
-      <c r="I53" s="12"/>
-    </row>
-    <row r="54" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G54" s="13" t="s">
-        <v>237</v>
+      <c r="G53" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H53" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="I53" s="9"/>
+    </row>
+    <row r="54" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="10"/>
+      <c r="B54" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>186</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="I54" s="9"/>
+        <v>183</v>
+      </c>
+      <c r="I54" s="12"/>
     </row>
     <row r="55" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A55" s="10"/>
       <c r="B55" s="14" t="s">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>238</v>
+        <v>191</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="H55" s="14" t="s">
-        <v>210</v>
+        <v>186</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>183</v>
       </c>
       <c r="I55" s="12"/>
     </row>
     <row r="56" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A56" s="10"/>
       <c r="B56" s="14" t="s">
-        <v>316</v>
+        <v>266</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>240</v>
+        <v>193</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>233</v>
+        <v>186</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>238</v>
+        <v>191</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="H56" s="14" t="s">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="I56" s="12"/>
     </row>
     <row r="57" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>353</v>
+        <v>285</v>
       </c>
       <c r="B57" s="13"/>
       <c r="C57" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E57" s="13" t="s">
+      <c r="F57" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F57" s="13" t="s">
-        <v>28</v>
-      </c>
       <c r="G57" s="13" t="s">
-        <v>242</v>
+        <v>195</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="9"/>
     </row>
     <row r="58" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>354</v>
+        <v>286</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>317</v>
+        <v>267</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>243</v>
+        <v>196</v>
       </c>
       <c r="E58" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F58" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F58" s="13" t="s">
+      <c r="G58" s="13" t="s">
         <v>30</v>
-      </c>
-      <c r="G58" s="13" t="s">
-        <v>31</v>
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="9"/>
@@ -3054,22 +3101,22 @@
     <row r="59" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A59" s="10"/>
       <c r="B59" s="14" t="s">
-        <v>318</v>
+        <v>268</v>
       </c>
       <c r="C59" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>244</v>
+        <v>197</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>245</v>
+        <v>198</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>247</v>
+        <v>200</v>
       </c>
       <c r="H59" s="14"/>
       <c r="I59" s="12"/>
@@ -3077,22 +3124,22 @@
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="10"/>
       <c r="B60" s="14" t="s">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="F60" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="F60" s="14" t="s">
+      <c r="G60" s="14" t="s">
         <v>34</v>
-      </c>
-      <c r="G60" s="14" t="s">
-        <v>35</v>
       </c>
       <c r="H60" s="14"/>
       <c r="I60" s="12"/>
@@ -3100,47 +3147,47 @@
     <row r="61" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A61" s="10"/>
       <c r="B61" s="14" t="s">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>248</v>
+        <v>201</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>249</v>
+        <v>202</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>250</v>
+        <v>203</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>251</v>
+        <v>204</v>
       </c>
       <c r="H61" s="14"/>
       <c r="I61" s="12"/>
     </row>
     <row r="62" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>355</v>
+        <v>287</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>321</v>
+        <v>271</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="F62" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E62" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="F62" s="13" t="s">
-        <v>37</v>
-      </c>
       <c r="G62" s="13" t="s">
-        <v>253</v>
+        <v>206</v>
       </c>
       <c r="H62" s="13"/>
       <c r="I62" s="9"/>
@@ -3148,22 +3195,22 @@
     <row r="63" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A63" s="10"/>
       <c r="B63" s="14" t="s">
-        <v>322</v>
+        <v>272</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E63" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E63" s="14" t="s">
+      <c r="F63" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F63" s="14" t="s">
-        <v>40</v>
-      </c>
       <c r="G63" s="14" t="s">
-        <v>254</v>
+        <v>207</v>
       </c>
       <c r="H63" s="14"/>
       <c r="I63" s="12"/>
@@ -3171,22 +3218,22 @@
     <row r="64" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A64" s="10"/>
       <c r="B64" s="14" t="s">
-        <v>323</v>
+        <v>273</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>255</v>
+        <v>208</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>256</v>
+        <v>209</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>257</v>
+        <v>210</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="H64" s="14"/>
       <c r="I64" s="12"/>
@@ -3194,19 +3241,19 @@
     <row r="65" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A65" s="10"/>
       <c r="B65" s="14" t="s">
-        <v>324</v>
+        <v>274</v>
       </c>
       <c r="C65" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>259</v>
+        <v>212</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>260</v>
+        <v>213</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>261</v>
+        <v>214</v>
       </c>
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
@@ -3214,25 +3261,25 @@
     </row>
     <row r="66" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>356</v>
+        <v>288</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E66" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E66" s="13" t="s">
+      <c r="F66" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F66" s="13" t="s">
+      <c r="G66" s="13" t="s">
         <v>43</v>
-      </c>
-      <c r="G66" s="13" t="s">
-        <v>44</v>
       </c>
       <c r="H66" s="13"/>
       <c r="I66" s="9"/>
@@ -3240,22 +3287,22 @@
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="10"/>
       <c r="B67" s="14" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
       <c r="C67" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E67" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="F67" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F67" s="14" t="s">
-        <v>47</v>
-      </c>
       <c r="G67" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H67" s="14"/>
       <c r="I67" s="12"/>
@@ -3263,22 +3310,22 @@
     <row r="68" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A68" s="10"/>
       <c r="B68" s="14" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>262</v>
+        <v>215</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>263</v>
+        <v>216</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>264</v>
+        <v>217</v>
       </c>
       <c r="G68" s="14" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="H68" s="14"/>
       <c r="I68" s="12"/>
@@ -3286,72 +3333,72 @@
     <row r="69" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10"/>
       <c r="B69" s="14" t="s">
-        <v>328</v>
+        <v>278</v>
       </c>
       <c r="C69" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E69" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="F69" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F69" s="14" t="s">
-        <v>50</v>
-      </c>
       <c r="G69" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H69" s="14"/>
       <c r="I69" s="12"/>
     </row>
     <row r="70" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>357</v>
+        <v>289</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>329</v>
+        <v>279</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>266</v>
+        <v>219</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>267</v>
+        <v>220</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>268</v>
+        <v>221</v>
       </c>
       <c r="H70" s="13"/>
       <c r="I70" s="9"/>
     </row>
     <row r="71" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>358</v>
+        <v>290</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>269</v>
+        <v>222</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>270</v>
+        <v>223</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>271</v>
+        <v>224</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>272</v>
+        <v>225</v>
       </c>
       <c r="H71" s="13"/>
       <c r="I71" s="9"/>
@@ -3359,22 +3406,22 @@
     <row r="72" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A72" s="10"/>
       <c r="B72" s="14" t="s">
-        <v>331</v>
+        <v>281</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>273</v>
+        <v>226</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>276</v>
+        <v>229</v>
       </c>
       <c r="H72" s="14"/>
       <c r="I72" s="12"/>

--- a/QCM1_1_CH.xlsx
+++ b/QCM1_1_CH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD772AF6-DA33-436D-8716-A62FD4064656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F96D21-7F48-4EE1-B26D-A2F43BD51611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="362">
   <si>
     <t>Question</t>
   </si>
@@ -132,9 +132,6 @@
     <t>acide méthanoïque</t>
   </si>
   <si>
-    <t>acide par une base.</t>
-  </si>
-  <si>
     <t>d'un acide par une base.</t>
   </si>
   <si>
@@ -660,18 +657,6 @@
     <t>$6,3\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$</t>
   </si>
   <si>
-    <t>$1,0\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$</t>
-  </si>
-  <si>
-    <t>$7$</t>
-  </si>
-  <si>
-    <t>$&lt; 7$</t>
-  </si>
-  <si>
-    <t>$&gt; 7$</t>
-  </si>
-  <si>
     <t>$2,5\cdot 10^{-3}\text{ mol}\cdot\text{L}^{-1}$</t>
   </si>
   <si>
@@ -693,18 +678,6 @@
     <t>7,6</t>
   </si>
   <si>
-    <t>$[Cl^-] = 10^{-1}\text{ mol}\cdot\text{m}^{-3}$</t>
-  </si>
-  <si>
-    <t>$[Cl^-] = 10^{-2}\text{ mol}\cdot\text{m}^{-3}$</t>
-  </si>
-  <si>
-    <t>$[Cl^-] = 10^{-3}\text{ mol}\cdot\text{m}^{-3}$</t>
-  </si>
-  <si>
-    <t>$[Cl^-] = 10^{-4}\text{ mol}\cdot\text{m}^{-3}$</t>
-  </si>
-  <si>
     <t>$10^{-3}\text{ S}\cdot\text{m}^{-1}$</t>
   </si>
   <si>
@@ -826,9 +799,6 @@
   </si>
   <si>
     <t>La concentration, à l'équilibre, en acide éthanoïque en $\text{mol}\cdot\text{L}^{-1}$ est :</t>
-  </si>
-  <si>
-    <t>En solution aqueuse :</t>
   </si>
   <si>
     <t>La masse molaire de l'acide est égale à :</t>
@@ -882,11 +852,6 @@
   <si>
     <t>&lt;center&gt;&lt;b&gt;Phénate de sodium et l'acide éthanoïque&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
 Dans 20 mL de solution de phénate de sodium à $0,2\text{ mol}\cdot\text{L}^{-1}$, on verse 10 mL d'acide éthanoïque à $0,2\text{ mol}\cdot\text{L}^{-1}$. A l'équilibre le pH vaut $10$.</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Nitrate de fer III&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-On veut préparer 250mL d'une solution aqueuse de nitrate de fer III telle que la concentration des ions nitrate soit égale à $0,6\text{ mol}\cdot\text{L}^{-1}$. Le sulfate de fer est totalement soluble. La masse de nitrate de fer III à dissoudre est égale à :
-Masse molaire en g/mol : Fe = 56 ; N = 14 ; O = 16</t>
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;Acide carboxylique HA&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
@@ -894,28 +859,9 @@
 Le pH de cette solution est de $3,4$.</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Dosage acido-basique&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-Lors d'un dosage acido-basique, on obtient la courbe ci-contre pH = f(V).
-On donne : $10^{0,2} = 1,6$ ; $10^{0,8} = 6,3$ ; $10^{-0,8} = 0,16$</t>
-  </si>
-  <si>
     <t>&lt;center&gt;&lt;b&gt;Le produit ionique de l'eau&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
 A 37°C, le produit ionique de l'eau est $K_e = 2,5\cdot 10^{-14}$. À 25°C, $pK_e = 14$.
 On donne : $\sqrt{10^{-15}} = 3,2\cdot 10^{-8}$.</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;La solution d'acide chlorhydrique commerciale&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-On dispose d'une solution d'acide chlorhydrique commerciale. Sur l'étiquette on lit :
-- $d = 1,19$
-- Pourcentage massique en chlorure d'hydrogène 36%
-- Masse molaire $M(HCl) = 36,5\text{ g}\cdot\text{mol}^{-1}$
-Calcul intermédiaire : $1,19 \times 0,36 = 4284\cdot 10^{-4}$ ; $4284 / 365 = 11,7$</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;La soude et l'acide chlorhydrique&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
-Un mélange de 2 litres de soude à $10^{-4}\text{ mol}\cdot\text{L}^{-1}$ et de 10 mL d'acide chlorhydrique à $2\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$.
-On donne les conductivités ioniques molaires ($\text{S}\cdot\text{m}^2\cdot\text{mol}^{-1}$) à 25 °C :
-$\lambda_{Na^+} = 5\cdot 10^{-3}$ ; $\lambda_{Cl^-} = 7,6\cdot 10^{-3}$ ; $\lambda_{HO^-} = 19,8\cdot 10^{-3}$ ; $\lambda_{H_3O^+} = 34,9\cdot 10^{-3}$.</t>
   </si>
   <si>
     <t>$AH_{(aq)} + A^-_{(aq)} \rightleftharpoons BH^+_{(aq)} + B^-_{(aq)}$</t>
@@ -1172,12 +1118,70 @@
   <si>
     <t>La concentration, à l'équilibre, en phénol en $\text{mol}\cdot\text{L}^{-1}$ est :</t>
   </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Nitrate de fer III&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On dispose de Nitrate de fer III solide $\mathrm{Fe(NO_3)_3(s)}$.
+On veut préparer 250mL d'une solution aqueuse de nitrate de fer III telle que la concentration des ions nitrate soit égale à $0,6\text{ mol}\cdot\text{L}^{-1}$. Le sulfate de fer est totalement soluble. 
+&lt;br&gt;Masse molaire en g/mol : Fe = 56 ; N = 14 ; O = 16</t>
+  </si>
+  <si>
+    <t>La masse de nitrate de fer III à dissoudre est égale à :</t>
+  </si>
+  <si>
+    <t>En solution aqueuse, cet acide  :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Dosage acido-basique&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+Lors d'un dosage acido-basique, on obtient la courbe ci-contre du pH = f(V).
+&lt;br&gt;On donne : $10^{0,2} = 1,6$ ; $10^{0,8} = 6,3$ ; $10^{-0,8} = 0,16$</t>
+  </si>
+  <si>
+    <t>d'une base par un acide</t>
+  </si>
+  <si>
+    <t>$1,0\cdot 10^{-7}\text{ mol}\cdot\text{L}^{-1}$</t>
+  </si>
+  <si>
+    <t>$pH_E = 7$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;La solution d'acide chlorhydrique commerciale&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On dispose d'une solution d'acide chlorhydrique commerciale. Sur l'étiquette on lit :
+&lt;br&gt; * $d = 1,19$
+&lt;br&gt; * Pourcentage massique en chlorure d'hydrogène 36%
+&lt;br&gt; * Masse molaire $M(HCl) = 36,5\text{ g}\cdot\text{mol}^{-1}$
+&lt;br&gt; Calcul intermédiaire : $1,19 \times 0,36 = 4284\cdot 10^{-4}$ ; $\quad$ $4284 / 365 = 11,7$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;La soude et l'acide chlorhydrique&lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+Un mélange de 2 litres de soude à $10^{-4}\text{ mol}\cdot\text{L}^{-1}$ et de 10 mL d'acide chlorhydrique à $2\cdot 10^{-2}\text{ mol}\cdot\text{L}^{-1}$.
+&lt;br&gt;On donne les conductivités ioniques molaires ($\text{S}\cdot\text{m}^2\cdot\text{mol}^{-1}$) à 25 °C :
+$\lambda_{Na^+} = 5\cdot 10^{-3}$ ; $\quad$ $\lambda_{Cl^-} = 7,6\cdot 10^{-3}$ ; $\quad$ $\lambda_{HO^-} = 19,8\cdot 10^{-3}$ ; $\quad$ $\lambda_{H_3O^+} = 34,9\cdot 10^{-3}$.</t>
+  </si>
+  <si>
+    <t>$[Cl^-] \approx 10^{-1}\text{ mol}\cdot\text{m}^{-3}$</t>
+  </si>
+  <si>
+    <t>$[Cl^-] \approx 10^{-2}\text{ mol}\cdot\text{m}^{-3}$</t>
+  </si>
+  <si>
+    <t>$[Cl^-] \approx 10^{-3}\text{ mol}\cdot\text{m}^{-3}$</t>
+  </si>
+  <si>
+    <t>$[Cl^-] \approx 10^{-4}\text{ mol}\cdot\text{m}^{-3}$</t>
+  </si>
+  <si>
+    <t>CH_QCM1_1_Q1.png</t>
+  </si>
+  <si>
+    <t>CH_QCM1_1_Q2.png</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1209,12 +1213,6 @@
     <font>
       <i/>
       <sz val="10"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF0070C0"/>
       <name val="Consolas"/>
     </font>
     <font>
@@ -1315,7 +1313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1339,17 +1337,11 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1707,1724 +1699,1876 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>51</v>
+        <v>272</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="13"/>
-      <c r="I2" s="9"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="J2" s="4"/>
       <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="14" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12" t="s">
+        <v>14</v>
+      </c>
       <c r="J3" s="6"/>
       <c r="K3" s="5"/>
     </row>
     <row r="4" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="14" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="14" t="s">
+      <c r="E4" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="F4" s="14" t="s">
+      <c r="G4" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="J4" s="4"/>
       <c r="K4" s="5"/>
     </row>
     <row r="5" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="F5" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="G5" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12" t="s">
+        <v>58</v>
+      </c>
       <c r="J5" s="6"/>
       <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:11" ht="51" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>294</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>296</v>
-      </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="12"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12" t="s">
+        <v>282</v>
+      </c>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
     </row>
     <row r="7" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
-      <c r="B7" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="14" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="F7" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="G7" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="14" t="s">
+      <c r="A8" s="9"/>
+      <c r="B8" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="F8" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="G8" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="G8" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12" t="s">
+        <v>65</v>
+      </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
     </row>
     <row r="9" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="14" t="s">
+      <c r="A9" s="9"/>
+      <c r="B9" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="F9" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="H9" s="14"/>
-      <c r="I9" s="12"/>
+      <c r="G9" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
     <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-      <c r="B10" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="14" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="F10" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="G10" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12" t="s">
+        <v>74</v>
+      </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="14" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="F11" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="G11" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12" t="s">
+        <v>76</v>
+      </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>235</v>
+        <v>273</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>226</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="9"/>
+      <c r="D12" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11" t="s">
+        <v>80</v>
+      </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
     </row>
     <row r="13" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
-      <c r="B13" s="13" t="s">
-        <v>298</v>
+      <c r="B13" s="11" t="s">
+        <v>284</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E13" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="9"/>
+      <c r="G13" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11" t="s">
+        <v>81</v>
+      </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
     </row>
     <row r="14" spans="1:11" ht="102" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
-      <c r="B14" s="13" t="s">
-        <v>299</v>
+      <c r="B14" s="11" t="s">
+        <v>285</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="F14" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="G14" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="9"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11" t="s">
+        <v>87</v>
+      </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
     </row>
     <row r="15" spans="1:11" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>237</v>
+        <v>286</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>228</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="9"/>
+      <c r="F15" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11" t="s">
+        <v>89</v>
+      </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
     </row>
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="14" t="s">
+      <c r="A16" s="9"/>
+      <c r="B16" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="F16" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="G16" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="G16" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="H16" s="14"/>
-      <c r="I16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12" t="s">
+        <v>90</v>
+      </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-      <c r="B17" s="14" t="s">
+    <row r="17" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="7"/>
+      <c r="B18" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="153" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="9"/>
+      <c r="B20" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="9"/>
+      <c r="B21" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="9"/>
+      <c r="B23" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="9"/>
+      <c r="B24" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="9"/>
+      <c r="B25" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="140.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="7"/>
+      <c r="B26" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="J26" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="9"/>
+      <c r="B27" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+      <c r="B28" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="102" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="H17" s="14"/>
-      <c r="I17" s="12"/>
-    </row>
-    <row r="18" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="9"/>
-    </row>
-    <row r="19" spans="1:9" ht="153" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B19" s="13" t="s">
+      <c r="C29" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+      <c r="B30" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A31" s="9"/>
+      <c r="B31" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="9"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="H20" s="14"/>
-      <c r="I20" s="12"/>
-    </row>
-    <row r="21" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="14" t="s">
+      <c r="C31" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="9"/>
+      <c r="B32" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H21" s="14"/>
-      <c r="I21" s="12"/>
-    </row>
-    <row r="22" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="B22" s="13" t="s">
+      <c r="C32" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A33" s="9"/>
+      <c r="B33" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="9"/>
-    </row>
-    <row r="23" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="B23" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="I23" s="12"/>
-    </row>
-    <row r="24" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="I24" s="12"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="I25" s="12"/>
-    </row>
-    <row r="26" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
-      <c r="B26" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="I26" s="9"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="I27" s="12"/>
-    </row>
-    <row r="28" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
-      <c r="B28" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="H28" s="14"/>
-      <c r="I28" s="12"/>
-    </row>
-    <row r="29" spans="1:9" ht="102" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="H29" s="13"/>
-      <c r="I29" s="9"/>
-    </row>
-    <row r="30" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
-      <c r="B30" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>328</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>329</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="H30" s="14"/>
-      <c r="I30" s="12"/>
-    </row>
-    <row r="31" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
-      <c r="B31" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>332</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="12"/>
-    </row>
-    <row r="32" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
-      <c r="B32" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="H32" s="14"/>
-      <c r="I32" s="12"/>
-    </row>
-    <row r="33" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="B33" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="14" t="s">
+      <c r="C33" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E33" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="F33" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="G33" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="G33" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="H33" s="14"/>
-      <c r="I33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="34" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A34" s="7"/>
-      <c r="B34" s="13" t="s">
-        <v>334</v>
+      <c r="B34" s="11" t="s">
+        <v>320</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E34" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="F34" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="G34" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="H34" s="11"/>
+      <c r="I34" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="9"/>
+      <c r="B35" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="51" x14ac:dyDescent="0.25">
+      <c r="A36" s="9"/>
+      <c r="B36" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="H34" s="13"/>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
-      <c r="B35" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="12"/>
-    </row>
-    <row r="36" spans="1:9" ht="51" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="B36" s="14" t="s">
-        <v>335</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="14" t="s">
+      <c r="E36" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="F36" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="G36" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="G36" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="H36" s="14"/>
-      <c r="I36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="37" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
-      <c r="B37" s="13" t="s">
-        <v>336</v>
+      <c r="B37" s="11" t="s">
+        <v>322</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="E37" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="F37" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
+      <c r="B38" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F37" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="H37" s="13"/>
-      <c r="I37" s="9"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
-      <c r="B38" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="14" t="s">
+      <c r="E38" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="F38" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="G38" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="G38" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="H38" s="14"/>
-      <c r="I38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="39" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="F39" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="E39" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="F39" s="14" t="s">
+      <c r="G39" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="G39" s="14" t="s">
+      <c r="H39" s="11"/>
+      <c r="I39" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="9"/>
+      <c r="B40" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="9"/>
+      <c r="B41" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="H39" s="13"/>
-      <c r="I39" s="9"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="H40" s="14"/>
-      <c r="I40" s="12"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-      <c r="B41" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="42" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>257</v>
+        <v>331</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>248</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D42" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E42" s="13" t="s">
+      <c r="D42" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F42" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F42" s="13" t="s">
+      <c r="G42" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="G42" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="H42" s="13"/>
-      <c r="I42" s="9"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="43" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A43" s="7"/>
-      <c r="B43" s="13" t="s">
-        <v>346</v>
+      <c r="B43" s="11" t="s">
+        <v>332</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F43" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E43" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="F43" s="13" t="s">
+      <c r="G43" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="H43" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="G43" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H43" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="I43" s="9"/>
+      <c r="I43" s="11" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="44" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
-      <c r="B44" s="13" t="s">
-        <v>347</v>
+      <c r="B44" s="11" t="s">
+        <v>333</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D44" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="F44" s="13" t="s">
+      <c r="D44" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G44" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="G44" s="13" t="s">
+      <c r="H44" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="H44" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="I44" s="9"/>
+      <c r="I44" s="11" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="45" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
-      <c r="B45" s="13" t="s">
-        <v>350</v>
+      <c r="B45" s="11" t="s">
+        <v>336</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D45" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="E45" s="13" t="s">
+      <c r="D45" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="F45" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="G45" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="G45" s="13" t="s">
+      <c r="H45" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="H45" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="I45" s="9"/>
+      <c r="I45" s="11" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="46" spans="1:9" ht="178.5" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="9"/>
+      <c r="B47" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="H47" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="9"/>
+      <c r="B48" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="H48" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="9"/>
+      <c r="B49" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="165.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="E51" s="11">
+        <v>45</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="H51" s="11">
+        <v>1</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="9"/>
+      <c r="B52" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I52" s="12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="9"/>
+      <c r="B54" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="G54" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="I54" s="12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="9"/>
+      <c r="B55" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="I55" s="12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A56" s="9"/>
+      <c r="B56" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="H56" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="102" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A59" s="9"/>
+      <c r="B59" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="9"/>
+      <c r="B60" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G60" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H60" s="12"/>
+      <c r="I60" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="9"/>
+      <c r="B61" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G62" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J62" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="9"/>
+      <c r="B63" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="9"/>
+      <c r="B64" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="G64" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="B46" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F46" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="G46" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="I46" s="9"/>
-    </row>
-    <row r="47" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="10"/>
-      <c r="B47" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="E47" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="F47" s="14" t="s">
+      <c r="H64" s="12"/>
+      <c r="I64" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="9"/>
+      <c r="B65" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E65" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="G47" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="H47" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="I47" s="12"/>
-    </row>
-    <row r="48" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="10"/>
-      <c r="B48" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="F48" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="I48" s="12"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="10"/>
-      <c r="B49" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="12"/>
-    </row>
-    <row r="50" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="G50" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="H50" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="I50" s="9"/>
-    </row>
-    <row r="51" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="E51" s="13">
-        <v>45</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="G51" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="H51" s="13">
-        <v>1</v>
-      </c>
-      <c r="I51" s="9"/>
-    </row>
-    <row r="52" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="10"/>
-      <c r="B52" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="F52" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="G52" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="H52" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="I52" s="12"/>
-    </row>
-    <row r="53" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="F53" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G53" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="H53" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="I53" s="9"/>
-    </row>
-    <row r="54" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="10"/>
-      <c r="B54" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E54" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="F54" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="G54" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="H54" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="I54" s="12"/>
-    </row>
-    <row r="55" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="10"/>
-      <c r="B55" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E55" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="F55" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="G55" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="H55" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="I55" s="12"/>
-    </row>
-    <row r="56" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A56" s="10"/>
-      <c r="B56" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="E56" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="F56" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="G56" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="H56" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="I56" s="12"/>
-    </row>
-    <row r="57" spans="1:9" ht="102" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F57" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G57" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="H57" s="13"/>
-      <c r="I57" s="9"/>
-    </row>
-    <row r="58" spans="1:9" ht="102" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F58" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="G58" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H58" s="13"/>
-      <c r="I58" s="9"/>
-    </row>
-    <row r="59" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="10"/>
-      <c r="B59" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="F59" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="G59" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="H59" s="14"/>
-      <c r="I59" s="12"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="10"/>
-      <c r="B60" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E60" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F60" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G60" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="H60" s="14"/>
-      <c r="I60" s="12"/>
-    </row>
-    <row r="61" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="10"/>
-      <c r="B61" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E61" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="F61" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="G61" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="H61" s="14"/>
-      <c r="I61" s="12"/>
-    </row>
-    <row r="62" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="F62" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G62" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="H62" s="13"/>
-      <c r="I62" s="9"/>
-    </row>
-    <row r="63" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="10"/>
-      <c r="B63" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E63" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="F63" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G63" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="H63" s="14"/>
-      <c r="I63" s="12"/>
-    </row>
-    <row r="64" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="10"/>
-      <c r="B64" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="E64" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="F64" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="G64" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="H64" s="14"/>
-      <c r="I64" s="12"/>
-    </row>
-    <row r="65" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="10"/>
-      <c r="B65" s="14" t="s">
-        <v>274</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="E65" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="F65" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="12"/>
+      <c r="F65" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="G65" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="H65" s="12"/>
+      <c r="I65" s="12" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="66" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>265</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D66" s="13" t="s">
+      <c r="D66" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E66" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E66" s="13" t="s">
+      <c r="F66" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F66" s="13" t="s">
+      <c r="G66" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G66" s="13" t="s">
+      <c r="H66" s="11"/>
+      <c r="I66" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="9"/>
+      <c r="B67" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="H66" s="13"/>
-      <c r="I66" s="9"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="10"/>
-      <c r="B67" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="14" t="s">
+      <c r="E67" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="F67" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F67" s="14" t="s">
+      <c r="G67" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="9"/>
+      <c r="B68" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="F68" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="G68" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="H68" s="12"/>
+      <c r="I68" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A69" s="9"/>
+      <c r="B69" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G67" s="14" t="s">
+      <c r="E69" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G69" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H67" s="14"/>
-      <c r="I67" s="12"/>
-    </row>
-    <row r="68" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="10"/>
-      <c r="B68" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" s="14" t="s">
+      <c r="H69" s="12"/>
+      <c r="I69" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F70" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="E68" s="14" t="s">
+      <c r="G70" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="F68" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="G68" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="H68" s="14"/>
-      <c r="I68" s="12"/>
-    </row>
-    <row r="69" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A69" s="10"/>
-      <c r="B69" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E69" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F69" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G69" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="H69" s="14"/>
-      <c r="I69" s="12"/>
-    </row>
-    <row r="70" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F70" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="G70" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="H70" s="13"/>
-      <c r="I70" s="9"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="11" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="71" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>280</v>
+        <v>355</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D71" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="F71" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="G71" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="H71" s="13"/>
-      <c r="I71" s="9"/>
+      <c r="D71" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="72" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="10"/>
-      <c r="B72" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="E72" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="F72" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="G72" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="H72" s="14"/>
-      <c r="I72" s="12"/>
+      <c r="A72" s="9"/>
+      <c r="B72" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="G72" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12" t="s">
+        <v>218</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
